--- a/week-01/Ex4A_GTrends_Marketing.xlsx
+++ b/week-01/Ex4A_GTrends_Marketing.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\angelosorio\Documents\DataAnalytics\week-01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ACFF2800-9CE7-41D6-954E-2C6CDE78F671}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0833372F-259F-48F8-AE34-FF9BB9E24286}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{424FF6AE-B0E6-40F4-A153-FF2E4F097C91}"/>
   </bookViews>
@@ -836,16 +836,77 @@
       <c:pivotFmt>
         <c:idx val="0"/>
         <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
+          <a:gradFill flip="none" rotWithShape="1">
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:schemeClr val="accent1"/>
+              </a:gs>
+              <a:gs pos="75000">
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                  <a:lumOff val="40000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="51000">
+                <a:schemeClr val="accent1">
+                  <a:alpha val="75000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="20000"/>
+                  <a:lumOff val="80000"/>
+                  <a:alpha val="15000"/>
+                </a:schemeClr>
+              </a:gs>
+            </a:gsLst>
+            <a:lin ang="5400000" scaled="0"/>
+          </a:gradFill>
           <a:ln>
             <a:noFill/>
           </a:ln>
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="none"/>
+          <c:symbol val="circle"/>
+          <c:size val="6"/>
+          <c:spPr>
+            <a:gradFill flip="none" rotWithShape="1">
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent1"/>
+                </a:gs>
+                <a:gs pos="75000">
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="60000"/>
+                    <a:lumOff val="40000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="51000">
+                  <a:schemeClr val="accent1">
+                    <a:alpha val="75000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="20000"/>
+                    <a:lumOff val="80000"/>
+                    <a:alpha val="15000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000" scaled="0"/>
+            </a:gradFill>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:shade val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -892,16 +953,77 @@
       <c:pivotFmt>
         <c:idx val="1"/>
         <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
+          <a:gradFill flip="none" rotWithShape="1">
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:schemeClr val="accent1"/>
+              </a:gs>
+              <a:gs pos="75000">
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                  <a:lumOff val="40000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="51000">
+                <a:schemeClr val="accent1">
+                  <a:alpha val="75000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="20000"/>
+                  <a:lumOff val="80000"/>
+                  <a:alpha val="15000"/>
+                </a:schemeClr>
+              </a:gs>
+            </a:gsLst>
+            <a:lin ang="5400000" scaled="0"/>
+          </a:gradFill>
           <a:ln>
             <a:noFill/>
           </a:ln>
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="none"/>
+          <c:symbol val="circle"/>
+          <c:size val="6"/>
+          <c:spPr>
+            <a:gradFill flip="none" rotWithShape="1">
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent2"/>
+                </a:gs>
+                <a:gs pos="75000">
+                  <a:schemeClr val="accent2">
+                    <a:lumMod val="60000"/>
+                    <a:lumOff val="40000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="51000">
+                  <a:schemeClr val="accent2">
+                    <a:alpha val="75000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent2">
+                    <a:lumMod val="20000"/>
+                    <a:lumOff val="80000"/>
+                    <a:alpha val="15000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000" scaled="0"/>
+            </a:gradFill>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:shade val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -967,9 +1089,32 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
+            <a:gradFill flip="none" rotWithShape="1">
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent1"/>
+                </a:gs>
+                <a:gs pos="75000">
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="60000"/>
+                    <a:lumOff val="40000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="51000">
+                  <a:schemeClr val="accent1">
+                    <a:alpha val="75000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="20000"/>
+                    <a:lumOff val="80000"/>
+                    <a:alpha val="15000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000" scaled="0"/>
+            </a:gradFill>
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1074,9 +1219,32 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent2"/>
-            </a:solidFill>
+            <a:gradFill flip="none" rotWithShape="1">
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent2"/>
+                </a:gs>
+                <a:gs pos="75000">
+                  <a:schemeClr val="accent2">
+                    <a:lumMod val="60000"/>
+                    <a:lumOff val="40000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="51000">
+                  <a:schemeClr val="accent2">
+                    <a:alpha val="75000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent2">
+                    <a:lumMod val="20000"/>
+                    <a:lumOff val="80000"/>
+                    <a:alpha val="15000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000" scaled="0"/>
+            </a:gradFill>
             <a:ln>
               <a:noFill/>
             </a:ln>
@@ -1174,8 +1342,8 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:gapWidth val="219"/>
-        <c:overlap val="-27"/>
+        <c:gapWidth val="355"/>
+        <c:overlap val="-70"/>
         <c:axId val="1589670159"/>
         <c:axId val="1589669679"/>
       </c:barChart>
@@ -1240,12 +1408,23 @@
         <c:majorGridlines>
           <c:spPr>
             <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
+              <a:gradFill>
+                <a:gsLst>
+                  <a:gs pos="100000">
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="5000"/>
+                      <a:lumOff val="95000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                  <a:gs pos="0">
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="25000"/>
+                      <a:lumOff val="75000"/>
+                    </a:schemeClr>
+                  </a:gs>
+                </a:gsLst>
+                <a:lin ang="5400000" scaled="0"/>
+              </a:gradFill>
               <a:round/>
             </a:ln>
             <a:effectLst/>
@@ -1426,7 +1605,7 @@
 </file>
 
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="210">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -1437,7 +1616,7 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:defRPr sz="900" kern="1200" cap="all"/>
   </cs:axisTitle>
   <cs:categoryAxis>
     <cs:lnRef idx="0"/>
@@ -1467,7 +1646,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
@@ -1483,7 +1662,7 @@
         <a:round/>
       </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:chartArea>
   <cs:dataLabel>
     <cs:lnRef idx="0"/>
@@ -1502,23 +1681,15 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
+      <a:schemeClr val="bg1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
-        <a:schemeClr val="lt1"/>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="50000"/>
+          <a:lumOff val="50000"/>
+        </a:schemeClr>
       </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
     </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
     <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
@@ -1527,32 +1698,88 @@
   </cs:dataLabelCallout>
   <cs:dataPoint>
     <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
+    <cs:fillRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:gradFill flip="none" rotWithShape="1">
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="phClr"/>
+          </a:gs>
+          <a:gs pos="75000">
+            <a:schemeClr val="phClr">
+              <a:lumMod val="60000"/>
+              <a:lumOff val="40000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="51000">
+            <a:schemeClr val="phClr">
+              <a:alpha val="75000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="phClr">
+              <a:lumMod val="20000"/>
+              <a:lumOff val="80000"/>
+              <a:alpha val="15000"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:lin ang="5400000" scaled="0"/>
+      </a:gradFill>
+    </cs:spPr>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
+    <cs:fillRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:gradFill flip="none" rotWithShape="1">
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="phClr"/>
+          </a:gs>
+          <a:gs pos="75000">
+            <a:schemeClr val="phClr">
+              <a:lumMod val="60000"/>
+              <a:lumOff val="40000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="51000">
+            <a:schemeClr val="phClr">
+              <a:alpha val="75000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="phClr">
+              <a:lumMod val="20000"/>
+              <a:lumOff val="80000"/>
+              <a:alpha val="15000"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:lin ang="5400000" scaled="0"/>
+      </a:gradFill>
+    </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1"/>
+    <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="28575" cap="rnd">
@@ -1567,30 +1794,59 @@
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1">
+    <cs:fillRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525">
+      <a:gradFill flip="none" rotWithShape="1">
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="phClr"/>
+          </a:gs>
+          <a:gs pos="75000">
+            <a:schemeClr val="phClr">
+              <a:lumMod val="60000"/>
+              <a:lumOff val="40000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="51000">
+            <a:schemeClr val="phClr">
+              <a:alpha val="75000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="phClr">
+              <a:lumMod val="20000"/>
+              <a:lumOff val="80000"/>
+              <a:alpha val="15000"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:lin ang="5400000" scaled="0"/>
+      </a:gradFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="phClr"/>
+          <a:schemeClr val="phClr">
+            <a:shade val="95000"/>
+          </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
   <cs:dataPointWireframe>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1"/>
+    <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="rnd">
@@ -1612,15 +1868,13 @@
       </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="15000"/>
             <a:lumOff val="85000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
@@ -1635,8 +1889,8 @@
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
         </a:schemeClr>
       </a:solidFill>
       <a:ln w="9525">
@@ -1654,17 +1908,16 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="35000"/>
             <a:lumOff val="65000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:dropLine>
@@ -1673,7 +1926,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
@@ -1692,30 +1945,35 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
   </cs:floor>
   <cs:gridlineMajor>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="100000">
+              <a:schemeClr val="tx1">
+                <a:lumMod val="5000"/>
+                <a:lumOff val="95000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="0">
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
         <a:round/>
       </a:ln>
     </cs:spPr>
@@ -1725,16 +1983,27 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="100000">
+              <a:schemeClr val="tx1">
+                <a:lumMod val="5000"/>
+                <a:lumOff val="95000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="0">
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
         <a:round/>
       </a:ln>
     </cs:spPr>
@@ -1744,17 +2013,16 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:hiLoLine>
@@ -1763,17 +2031,16 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="35000"/>
             <a:lumOff val="65000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:leaderLine>
@@ -1794,7 +2061,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
   </cs:plotArea>
   <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
@@ -1802,7 +2069,7 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
   </cs:plotArea3D>
   <cs:seriesAxis>
@@ -1815,6 +2082,19 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+        <a:headEnd type="none" w="sm" len="sm"/>
+        <a:tailEnd type="none" w="sm" len="sm"/>
+      </a:ln>
+    </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:seriesAxis>
   <cs:seriesLine>
@@ -1822,10 +2102,10 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="35000"/>
@@ -1846,7 +2126,7 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+    <cs:defRPr sz="1800" b="1" kern="1200" cap="all" spc="50" baseline="0"/>
   </cs:title>
   <cs:trendline>
     <cs:lnRef idx="0">
@@ -1855,14 +2135,13 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="19050" cap="rnd">
+      <a:ln w="9525" cap="rnd">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:prstDash val="sysDot"/>
       </a:ln>
     </cs:spPr>
   </cs:trendline>
@@ -1892,8 +2171,8 @@
       <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
       </a:ln>
@@ -1916,14 +2195,8 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
   </cs:wall>
 </cs:chartStyle>
 </file>
@@ -2076,7 +2349,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CAE63B72-E0F3-4E4F-A435-270F986E33AA}" name="PivotTable1" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CAE63B72-E0F3-4E4F-A435-270F986E33AA}" name="PivotTable1" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
   <location ref="A15:C26" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="4">
     <pivotField axis="axisRow" showAll="0">
